--- a/WorldCupSweep_Part1_Form.xlsx
+++ b/WorldCupSweep_Part1_Form.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ofrewin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\WC_Sweepstake\world_cup_2026_sweepstake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7418A0-115F-49DB-86DB-A2741EB489E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3713F38-6D18-44B6-BACB-D4C67BF380AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="My Predictions" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,12 @@
   <definedNames>
     <definedName name="TeamList">_TeamList!$A$1:$A$48</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -47,7 +52,7 @@
     <t>3. Use the orange cells to lock in your four bonus picks (finalists, winner, top scorer).</t>
   </si>
   <si>
-    <t>4. Save the file as 'WorldCupSweep_&lt;YourName&gt;.xlsx' and send back to the organiser before kick-off.</t>
+    <t>4. Save the file as 'WorldCupSweep_Part1_Form_&lt;YourName&gt;.xlsx' and send back to the organiser before kick-off.</t>
   </si>
   <si>
     <t>Scoring reminder</t>
@@ -215,148 +220,148 @@
     <t>(organiser email)</t>
   </si>
   <si>
+    <t>Algeria</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Cape Verde</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Curaçao</t>
+  </si>
+  <si>
+    <t>Czech Republic</t>
+  </si>
+  <si>
+    <t>DR Congo</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>Iran</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>Ivory Coast</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
     <t>Mexico</t>
   </si>
   <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Scotland</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
     <t>South Africa</t>
   </si>
   <si>
     <t>South Korea</t>
   </si>
   <si>
-    <t>Czech Republic</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina</t>
-  </si>
-  <si>
-    <t>Qatar</t>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Sweden</t>
   </si>
   <si>
     <t>Switzerland</t>
   </si>
   <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>Morocco</t>
-  </si>
-  <si>
-    <t>Haiti</t>
-  </si>
-  <si>
-    <t>Scotland</t>
+    <t>Tunisia</t>
+  </si>
+  <si>
+    <t>Türkiye</t>
   </si>
   <si>
     <t>United States</t>
   </si>
   <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Türkiye</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>Curaçao</t>
-  </si>
-  <si>
-    <t>Ivory Coast</t>
-  </si>
-  <si>
-    <t>Ecuador</t>
-  </si>
-  <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Sweden</t>
-  </si>
-  <si>
-    <t>Tunisia</t>
-  </si>
-  <si>
-    <t>Belgium</t>
-  </si>
-  <si>
-    <t>Egypt</t>
-  </si>
-  <si>
-    <t>Iran</t>
-  </si>
-  <si>
-    <t>New Zealand</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>Cape Verde</t>
-  </si>
-  <si>
-    <t>Saudi Arabia</t>
-  </si>
-  <si>
     <t>Uruguay</t>
   </si>
   <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>Senegal</t>
-  </si>
-  <si>
-    <t>Iraq</t>
-  </si>
-  <si>
-    <t>Norway</t>
-  </si>
-  <si>
-    <t>Argentina</t>
-  </si>
-  <si>
-    <t>Algeria</t>
-  </si>
-  <si>
-    <t>Austria</t>
-  </si>
-  <si>
-    <t>Jordan</t>
-  </si>
-  <si>
-    <t>Portugal</t>
-  </si>
-  <si>
-    <t>DR Congo</t>
-  </si>
-  <si>
     <t>Uzbekistan</t>
-  </si>
-  <si>
-    <t>Colombia</t>
-  </si>
-  <si>
-    <t>England</t>
-  </si>
-  <si>
-    <t>Croatia</t>
-  </si>
-  <si>
-    <t>Ghana</t>
-  </si>
-  <si>
-    <t>Panama</t>
   </si>
 </sst>
 </file>
@@ -369,57 +374,66 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -432,30 +446,35 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
+        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFE4B5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE4B5"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -478,36 +497,34 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -537,37 +554,80 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFBFBFBF"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFE2EFDA"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFE4B5"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF595959"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF1F3864"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -584,10 +644,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -625,234 +685,128 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -868,728 +822,742 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="49.5703125" customWidth="1"/>
+    <col min="2" max="2" width="49.59765625" customWidth="1"/>
     <col min="3" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="24" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="15"/>
-    </row>
-    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+    </row>
+    <row r="6" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-    </row>
-    <row r="12" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="12" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A15" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A16" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-    </row>
-    <row r="21" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="21" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-    </row>
-    <row r="24" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+    </row>
+    <row r="24" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-    </row>
-    <row r="25" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+    </row>
+    <row r="25" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-    </row>
-    <row r="26" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+    </row>
+    <row r="26" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-    </row>
-    <row r="27" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+    </row>
+    <row r="27" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-    </row>
-    <row r="28" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+    </row>
+    <row r="28" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-    </row>
-    <row r="29" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+    </row>
+    <row r="29" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-    </row>
-    <row r="30" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+    </row>
+    <row r="30" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-    </row>
-    <row r="31" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+    </row>
+    <row r="31" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-    </row>
-    <row r="32" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+    </row>
+    <row r="32" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-    </row>
-    <row r="33" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+    </row>
+    <row r="33" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-    </row>
-    <row r="34" spans="1:5" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+    </row>
+    <row r="34" spans="1:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-    </row>
-    <row r="37" spans="1:5" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+    </row>
+    <row r="37" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="21"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="4" t="s">
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="16" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="10" t="s">
+    <row r="40" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="11">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="23">
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="10" t="s">
+    <row r="41" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="11">
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="23">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="10" t="s">
+    <row r="42" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="11">
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="23">
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="10" t="s">
+    <row r="43" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="11">
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="23">
         <v>15</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="18" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="15"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A48" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B48" s="25" t="s">
+      <c r="B48" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="26">
     <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="A8:E8"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A9:E9"/>
     <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B43:D43"/>
-    <mergeCell ref="B39:D39"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="B42:D42"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B15:E15"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B4:E4"/>
     <mergeCell ref="A6:E6"/>
-    <mergeCell ref="B4:E4"/>
     <mergeCell ref="A7:E7"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B41:D41"/>
   </mergeCells>
   <dataValidations count="13">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C23 D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Mexico,South Africa,South Korea,Czech Republic"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C23:D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
+      <formula1>"Czech Republic,Mexico,South Africa,South Korea"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C24 D24" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"Canada,Bosnia and Herzegovina,Qatar,Switzerland"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C24:D24" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"Bosnia and Herzegovina,Canada,Qatar,Switzerland"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C25 D25" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"Brazil,Morocco,Haiti,Scotland"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000002000000}">
+      <formula1>"Brazil,Haiti,Morocco,Scotland"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C26 D26" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>"United States,Paraguay,Australia,Türkiye"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C26:D26" xr:uid="{00000000-0002-0000-0000-000003000000}">
+      <formula1>"Australia,Paraguay,Türkiye,United States"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C27 D27" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>"Germany,Curaçao,Ivory Coast,Ecuador"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C27:D27" xr:uid="{00000000-0002-0000-0000-000004000000}">
+      <formula1>"Curaçao,Ecuador,Germany,Ivory Coast"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C28 D28" xr:uid="{00000000-0002-0000-0000-000005000000}">
-      <formula1>"Netherlands,Japan,Sweden,Tunisia"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C28:D28" xr:uid="{00000000-0002-0000-0000-000005000000}">
+      <formula1>"Japan,Netherlands,Sweden,Tunisia"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C29 D29" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C29:D29" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"Belgium,Egypt,Iran,New Zealand"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C30 D30" xr:uid="{00000000-0002-0000-0000-000007000000}">
-      <formula1>"Spain,Cape Verde,Saudi Arabia,Uruguay"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C30:D30" xr:uid="{00000000-0002-0000-0000-000007000000}">
+      <formula1>"Cape Verde,Saudi Arabia,Spain,Uruguay"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C31 D31" xr:uid="{00000000-0002-0000-0000-000008000000}">
-      <formula1>"France,Senegal,Iraq,Norway"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C31:D31" xr:uid="{00000000-0002-0000-0000-000008000000}">
+      <formula1>"France,Iraq,Norway,Senegal"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C32 D32" xr:uid="{00000000-0002-0000-0000-000009000000}">
-      <formula1>"Argentina,Algeria,Austria,Jordan"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C32:D32" xr:uid="{00000000-0002-0000-0000-000009000000}">
+      <formula1>"Algeria,Argentina,Austria,Jordan"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C33 D33" xr:uid="{00000000-0002-0000-0000-00000A000000}">
-      <formula1>"Portugal,DR Congo,Uzbekistan,Colombia"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C33:D33" xr:uid="{00000000-0002-0000-0000-00000A000000}">
+      <formula1>"Colombia,DR Congo,Portugal,Uzbekistan"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C34 D34" xr:uid="{00000000-0002-0000-0000-00000B000000}">
-      <formula1>"England,Croatia,Ghana,Panama"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick from this group" error="Please select one of the four teams in this group." sqref="C34:D34" xr:uid="{00000000-0002-0000-0000-00000B000000}">
+      <formula1>"Croatia,England,Ghana,Panama"</formula1>
+      <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Pick a team" error="Please select one of the 48 teams." sqref="B40:B42" xr:uid="{00000000-0002-0000-0000-00000C000000}">
       <formula1>TeamList</formula1>
+      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0"/>
+  <pageMargins left="0.5" right="0.5" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>